--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_software_system_application.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_software_system_application.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-2.635658914728682</v>
+        <v>-2.098484848484849</v>
       </c>
       <c r="H2">
-        <v>-2.635658914728682</v>
+        <v>-2.098484848484849</v>
       </c>
       <c r="I2">
-        <v>-1.288759689922481</v>
+        <v>-2.128787878787879</v>
       </c>
       <c r="J2">
-        <v>-1.288759689922481</v>
+        <v>-2.128787878787879</v>
       </c>
       <c r="K2">
-        <v>-0.605</v>
+        <v>-0.996</v>
       </c>
       <c r="L2">
-        <v>-1.172480620155039</v>
+        <v>-3.772727272727272</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.07</v>
+        <v>0.414</v>
       </c>
       <c r="V2">
-        <v>0.1445945945945946</v>
+        <v>0.1004854368932039</v>
       </c>
       <c r="W2">
-        <v>-0.4481481481481481</v>
+        <v>-1.717241379310345</v>
       </c>
       <c r="X2">
-        <v>0.1402345829284804</v>
+        <v>0.120037303952232</v>
       </c>
       <c r="Y2">
-        <v>-0.5883827310766285</v>
+        <v>-1.837278683262577</v>
       </c>
       <c r="Z2">
-        <v>2.205128205128203</v>
+        <v>0.8888888888888892</v>
       </c>
       <c r="AA2">
-        <v>-2.841880341880339</v>
+        <v>-1.892255892255893</v>
       </c>
       <c r="AB2">
-        <v>0.1331114582697253</v>
+        <v>0.1117443150509358</v>
       </c>
       <c r="AC2">
-        <v>-2.974991800150065</v>
+        <v>-2.004000207306829</v>
       </c>
       <c r="AD2">
-        <v>0.787</v>
+        <v>0.661</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.787</v>
+        <v>0.661</v>
       </c>
       <c r="AG2">
-        <v>-0.283</v>
+        <v>0.2470000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.09612800781727128</v>
+        <v>0.1382555950637942</v>
       </c>
       <c r="AI2">
-        <v>0.5757132406730067</v>
+        <v>1.712435233160622</v>
       </c>
       <c r="AJ2">
-        <v>-0.03976394548264719</v>
+        <v>0.0565605678955805</v>
       </c>
       <c r="AK2">
-        <v>-0.9528619528619532</v>
+        <v>-8.821428571428584</v>
       </c>
       <c r="AL2">
-        <v>0.013</v>
+        <v>0.058</v>
       </c>
       <c r="AM2">
-        <v>0.002</v>
+        <v>0.058</v>
       </c>
       <c r="AN2">
-        <v>-1.402852049910873</v>
+        <v>-1.078303425774878</v>
       </c>
       <c r="AO2">
-        <v>-51.15384615384616</v>
+        <v>-9.689655172413794</v>
       </c>
       <c r="AP2">
-        <v>0.5044563279857398</v>
+        <v>-0.402936378466558</v>
       </c>
       <c r="AQ2">
-        <v>-332.5</v>
+        <v>-9.689655172413794</v>
       </c>
     </row>
     <row r="3">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-2.635658914728682</v>
+        <v>-2.098484848484849</v>
       </c>
       <c r="H3">
-        <v>-2.635658914728682</v>
+        <v>-2.098484848484849</v>
       </c>
       <c r="I3">
-        <v>-1.288759689922481</v>
+        <v>-2.128787878787879</v>
       </c>
       <c r="J3">
-        <v>-1.288759689922481</v>
+        <v>-2.128787878787879</v>
       </c>
       <c r="K3">
-        <v>-0.605</v>
+        <v>-0.996</v>
       </c>
       <c r="L3">
-        <v>-1.172480620155039</v>
+        <v>-3.772727272727272</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.07</v>
+        <v>0.414</v>
       </c>
       <c r="V3">
-        <v>0.1445945945945946</v>
+        <v>0.1004854368932039</v>
       </c>
       <c r="W3">
-        <v>-0.4481481481481481</v>
+        <v>-1.717241379310345</v>
       </c>
       <c r="X3">
-        <v>0.1402345829284804</v>
+        <v>0.120037303952232</v>
       </c>
       <c r="Y3">
-        <v>-0.5883827310766285</v>
+        <v>-1.837278683262577</v>
       </c>
       <c r="Z3">
-        <v>2.205128205128203</v>
+        <v>0.8888888888888892</v>
       </c>
       <c r="AA3">
-        <v>-2.841880341880339</v>
+        <v>-1.892255892255893</v>
       </c>
       <c r="AB3">
-        <v>0.1331114582697253</v>
+        <v>0.1117443150509358</v>
       </c>
       <c r="AC3">
-        <v>-2.974991800150065</v>
+        <v>-2.004000207306829</v>
       </c>
       <c r="AD3">
-        <v>0.787</v>
+        <v>0.661</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.787</v>
+        <v>0.661</v>
       </c>
       <c r="AG3">
-        <v>-0.283</v>
+        <v>0.2470000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.09612800781727128</v>
+        <v>0.1382555950637942</v>
       </c>
       <c r="AI3">
-        <v>0.5757132406730067</v>
+        <v>1.712435233160622</v>
       </c>
       <c r="AJ3">
-        <v>-0.03976394548264719</v>
+        <v>0.0565605678955805</v>
       </c>
       <c r="AK3">
-        <v>-0.9528619528619532</v>
+        <v>-8.821428571428584</v>
       </c>
       <c r="AL3">
-        <v>0.013</v>
+        <v>0.058</v>
       </c>
       <c r="AM3">
-        <v>0.002</v>
+        <v>0.058</v>
       </c>
       <c r="AN3">
-        <v>-1.402852049910873</v>
+        <v>-1.078303425774878</v>
       </c>
       <c r="AO3">
-        <v>-51.15384615384616</v>
+        <v>-9.689655172413794</v>
       </c>
       <c r="AP3">
-        <v>0.5044563279857398</v>
+        <v>-0.402936378466558</v>
       </c>
       <c r="AQ3">
-        <v>-332.5</v>
+        <v>-9.689655172413794</v>
       </c>
     </row>
   </sheetData>
